--- a/ELITE GYMNASTICS_2026-05-03_Girls_results.xlsx
+++ b/ELITE GYMNASTICS_2026-05-03_Girls_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/3rd MAY N IRELAND 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{25B711D8-A33E-4E64-925B-2B45846A56EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D394CA-0D7B-4022-BD04-0BF7EBABFCED}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{25B711D8-A33E-4E64-925B-2B45846A56EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4595D12-6311-4131-BDB5-E7614BCED079}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A26537C2-571E-4818-BFCE-6D644A57211F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{A26537C2-571E-4818-BFCE-6D644A57211F}"/>
   </bookViews>
   <sheets>
     <sheet name="Vault" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="111">
   <si>
     <t>Member ID</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>11.500</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Girls</t>
   </si>
 </sst>
 </file>
@@ -745,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32392E82-2DEE-478D-AB09-08B34AB3CD13}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -758,7 +764,7 @@
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -783,8 +789,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -809,8 +818,11 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -835,8 +847,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -861,8 +876,11 @@
       <c r="H4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -887,8 +905,11 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -913,8 +934,11 @@
       <c r="H6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -939,8 +963,11 @@
       <c r="H7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -965,8 +992,11 @@
       <c r="H8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -991,8 +1021,11 @@
       <c r="H9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1017,8 +1050,11 @@
       <c r="H10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1043,8 +1079,11 @@
       <c r="H11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1069,8 +1108,11 @@
       <c r="H12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1095,8 +1137,11 @@
       <c r="H13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1121,8 +1166,11 @@
       <c r="H14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1147,8 +1195,11 @@
       <c r="H15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1173,8 +1224,11 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1199,8 +1253,11 @@
       <c r="H17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1225,8 +1282,11 @@
       <c r="H18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1251,8 +1311,11 @@
       <c r="H19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1277,8 +1340,11 @@
       <c r="H20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1303,8 +1369,11 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1329,8 +1398,11 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1355,8 +1427,11 @@
       <c r="H23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1381,8 +1456,11 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1407,8 +1485,11 @@
       <c r="H25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -1433,8 +1514,11 @@
       <c r="H26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1459,8 +1543,11 @@
       <c r="H27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1485,8 +1572,11 @@
       <c r="H28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -1511,8 +1601,11 @@
       <c r="H29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1537,8 +1630,11 @@
       <c r="H30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1563,8 +1659,11 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1589,8 +1688,11 @@
       <c r="H32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1615,8 +1717,11 @@
       <c r="H33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -1641,8 +1746,11 @@
       <c r="H34" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -1667,8 +1775,11 @@
       <c r="H35" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1693,8 +1804,11 @@
       <c r="H36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1719,8 +1833,11 @@
       <c r="H37" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1745,8 +1862,11 @@
       <c r="H38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -1771,8 +1891,11 @@
       <c r="H39" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -1797,8 +1920,11 @@
       <c r="H40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -1823,8 +1949,11 @@
       <c r="H41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1849,8 +1978,11 @@
       <c r="H42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1875,8 +2007,11 @@
       <c r="H43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -1900,6 +2035,9 @@
       </c>
       <c r="H44" t="s">
         <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1909,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653C4EAF-1F3F-4DB7-9AF6-55971D95BB02}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -1922,7 +2060,7 @@
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1947,8 +2085,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1973,8 +2114,11 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1999,8 +2143,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2025,8 +2172,11 @@
       <c r="H4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -2051,8 +2201,11 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -2077,8 +2230,11 @@
       <c r="H6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2103,8 +2259,11 @@
       <c r="H7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2129,8 +2288,11 @@
       <c r="H8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2155,8 +2317,11 @@
       <c r="H9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -2181,8 +2346,11 @@
       <c r="H10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -2207,8 +2375,11 @@
       <c r="H11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2233,8 +2404,11 @@
       <c r="H12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2259,8 +2433,11 @@
       <c r="H13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2285,8 +2462,11 @@
       <c r="H14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2311,8 +2491,11 @@
       <c r="H15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2337,8 +2520,11 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -2363,8 +2549,11 @@
       <c r="H17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -2389,8 +2578,11 @@
       <c r="H18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2415,8 +2607,11 @@
       <c r="H19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -2441,8 +2636,11 @@
       <c r="H20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -2467,8 +2665,11 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -2493,8 +2694,11 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2519,8 +2723,11 @@
       <c r="H23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -2545,8 +2752,11 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -2571,8 +2781,11 @@
       <c r="H25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -2597,8 +2810,11 @@
       <c r="H26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -2623,8 +2839,11 @@
       <c r="H27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -2649,8 +2868,11 @@
       <c r="H28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2675,8 +2897,11 @@
       <c r="H29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -2701,8 +2926,11 @@
       <c r="H30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -2727,8 +2955,11 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -2753,8 +2984,11 @@
       <c r="H32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -2779,8 +3013,11 @@
       <c r="H33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -2805,8 +3042,11 @@
       <c r="H34" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2831,8 +3071,11 @@
       <c r="H35" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -2857,8 +3100,11 @@
       <c r="H36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -2883,8 +3129,11 @@
       <c r="H37" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2909,8 +3158,11 @@
       <c r="H38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2935,8 +3187,11 @@
       <c r="H39" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -2961,8 +3216,11 @@
       <c r="H40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -2987,8 +3245,11 @@
       <c r="H41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -3013,8 +3274,11 @@
       <c r="H42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -3039,8 +3303,11 @@
       <c r="H43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -3064,6 +3331,9 @@
       </c>
       <c r="H44" t="s">
         <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3073,7 +3343,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477B90A6-F027-417F-A005-CDE7872EE1D0}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -3086,7 +3356,7 @@
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3111,8 +3381,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3137,8 +3410,11 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3163,8 +3439,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3189,8 +3468,11 @@
       <c r="H4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3215,8 +3497,11 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3241,8 +3526,11 @@
       <c r="H6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -3267,8 +3555,11 @@
       <c r="H7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -3293,8 +3584,11 @@
       <c r="H8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -3319,8 +3613,11 @@
       <c r="H9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3345,8 +3642,11 @@
       <c r="H10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -3371,8 +3671,11 @@
       <c r="H11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -3397,8 +3700,11 @@
       <c r="H12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -3423,8 +3729,11 @@
       <c r="H13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -3449,8 +3758,11 @@
       <c r="H14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -3475,8 +3787,11 @@
       <c r="H15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -3501,8 +3816,11 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -3527,8 +3845,11 @@
       <c r="H17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -3553,8 +3874,11 @@
       <c r="H18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -3579,8 +3903,11 @@
       <c r="H19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -3605,8 +3932,11 @@
       <c r="H20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -3631,8 +3961,11 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -3657,8 +3990,11 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -3683,8 +4019,11 @@
       <c r="H23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -3709,8 +4048,11 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -3735,8 +4077,11 @@
       <c r="H25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -3761,8 +4106,11 @@
       <c r="H26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -3787,8 +4135,11 @@
       <c r="H27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -3813,8 +4164,11 @@
       <c r="H28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -3839,8 +4193,11 @@
       <c r="H29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -3865,8 +4222,11 @@
       <c r="H30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -3891,8 +4251,11 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4280,11 @@
       <c r="H32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -3943,8 +4309,11 @@
       <c r="H33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -3969,8 +4338,11 @@
       <c r="H34" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -3995,8 +4367,11 @@
       <c r="H35" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -4021,8 +4396,11 @@
       <c r="H36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -4047,8 +4425,11 @@
       <c r="H37" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -4073,8 +4454,11 @@
       <c r="H38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -4099,8 +4483,11 @@
       <c r="H39" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -4125,8 +4512,11 @@
       <c r="H40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -4151,8 +4541,11 @@
       <c r="H41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -4177,8 +4570,11 @@
       <c r="H42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -4203,8 +4599,11 @@
       <c r="H43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -4228,6 +4627,9 @@
       </c>
       <c r="H44" t="s">
         <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4237,7 +4639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BD3FBF-2E78-4FEC-A147-DBE07427BBCE}">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
@@ -4250,7 +4652,7 @@
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4275,8 +4677,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4301,8 +4706,11 @@
       <c r="H2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4327,8 +4735,11 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -4353,8 +4764,11 @@
       <c r="H4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -4379,8 +4793,11 @@
       <c r="H5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -4405,8 +4822,11 @@
       <c r="H6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -4431,8 +4851,11 @@
       <c r="H7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -4457,8 +4880,11 @@
       <c r="H8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -4483,8 +4909,11 @@
       <c r="H9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -4509,8 +4938,11 @@
       <c r="H10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -4535,8 +4967,11 @@
       <c r="H11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -4561,8 +4996,11 @@
       <c r="H12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -4587,8 +5025,11 @@
       <c r="H13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -4613,8 +5054,11 @@
       <c r="H14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -4639,8 +5083,11 @@
       <c r="H15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4665,8 +5112,11 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -4691,8 +5141,11 @@
       <c r="H17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -4717,8 +5170,11 @@
       <c r="H18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -4743,8 +5199,11 @@
       <c r="H19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -4769,8 +5228,11 @@
       <c r="H20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -4795,8 +5257,11 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -4821,8 +5286,11 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -4847,8 +5315,11 @@
       <c r="H23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -4873,8 +5344,11 @@
       <c r="H24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -4899,8 +5373,11 @@
       <c r="H25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -4925,8 +5402,11 @@
       <c r="H26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -4951,8 +5431,11 @@
       <c r="H27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -4977,8 +5460,11 @@
       <c r="H28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -5003,8 +5489,11 @@
       <c r="H29" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -5029,8 +5518,11 @@
       <c r="H30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -5055,8 +5547,11 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -5081,8 +5576,11 @@
       <c r="H32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -5107,8 +5605,11 @@
       <c r="H33" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -5133,8 +5634,11 @@
       <c r="H34" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -5159,8 +5663,11 @@
       <c r="H35" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -5185,8 +5692,11 @@
       <c r="H36" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -5211,8 +5721,11 @@
       <c r="H37" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -5237,8 +5750,11 @@
       <c r="H38" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -5263,8 +5779,11 @@
       <c r="H39" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -5289,8 +5808,11 @@
       <c r="H40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5837,11 @@
       <c r="H41" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>81</v>
       </c>
@@ -5341,8 +5866,11 @@
       <c r="H42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>90</v>
       </c>
@@ -5367,8 +5895,11 @@
       <c r="H43" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -5392,6 +5923,9 @@
       </c>
       <c r="H44" t="s">
         <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
